--- a/backend/data/IND5003_Regression.xlsx
+++ b/backend/data/IND5003_Regression.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124B4822-386E-A641-81DA-839FA6D5E16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E71933F-E601-8040-914C-7DEFD85E9FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16660" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="135">
-  <si>
-    <t>Context ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="77">
   <si>
     <t>Context Text</t>
   </si>
@@ -396,314 +393,7 @@
     <t>Regression, Basic Concepts in Statistics</t>
   </si>
   <si>
-    <t>Which of the following is an example of a classification problem?</t>
-  </si>
-  <si>
-    <t>Predicting tomorrow’s stock price based on today’s price.</t>
-  </si>
-  <si>
-    <t>Predicting the rental price of an apartment.</t>
-  </si>
-  <si>
-    <t>Identifying whether a tumor is present in an MRI scan.</t>
-  </si>
-  <si>
-    <t>Estimating how much a customer will spend on their next purchase.</t>
-  </si>
-  <si>
-    <t>A, B, D: Regression
-C: Classification</t>
-  </si>
-  <si>
-    <t>Which preprocessing technique is suitable when your dataset contains categorical variables?</t>
-  </si>
-  <si>
-    <t>Scaling</t>
-  </si>
-  <si>
-    <t>Principal Component Analysis (PCA)</t>
-  </si>
-  <si>
-    <t>One-Hot Encoding</t>
-  </si>
-  <si>
-    <t>Feature Extraction</t>
-  </si>
-  <si>
-    <t>A is for converting transforming numerical variables to have the same scale.
-B is used for:
-  * dimension reduction - reducing the number of continuous variables to a smaller subset, that 
-    consists of linear combinations of the original ones.
-  * removing correlation between numeric variables - this can improve prediction.
-C converts a single column containing the character version of the categorical
-  variable into a set of 0/1 columns representing it. ML methods require numeric inputs..
-D is a process whereby only important columns for prediction are retained.</t>
-  </si>
-  <si>
-    <t>Supervised Learning, Basic Concepts in Statistics</t>
-  </si>
-  <si>
-    <t>Data Manipulation, Supervised Learning</t>
-  </si>
-  <si>
-    <t>What is the shape of the *training dataset* (without the labels) when the following 
-code is executed?
-```{python eval=FALSE}
-from sklearn.model_selection import train_test_split
-import numpy as np
-# Generate sample data
-X = np.random.rand(100, 5)  
-y = np.random.randint(0, 2, 100)  
-X_train, X_test, y_train, y_test = train_test_split(X, y, test_size=0.2, random_state=42)
-print(X_train.shape)
-```</t>
-  </si>
-  <si>
-    <t>(80, 5)</t>
-  </si>
-  <si>
-    <t>(100, 5)</t>
-  </si>
-  <si>
-    <t>(20, 5)</t>
-  </si>
-  <si>
-    <t>(80, 2)</t>
-  </si>
-  <si>
-    <t>Which method in scikit-learn estimators is used to estimate the parameters of a model using the training data?</t>
-  </si>
-  <si>
-    <t>`fit()`</t>
-  </si>
-  <si>
-    <t>`predict()`</t>
-  </si>
-  <si>
-    <t>* `score()`</t>
-  </si>
-  <si>
-    <t>* `transform()`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A: True
-B: This is used *after* fitting; to make predictions.
-C: This returns the *score* (e.g. $R^2$ or RMSE) on a new dataset, after fitting has been done.
-D: This is also only called *after* fitting: to transform a dataset, e.g. scaling, PCA, etc. </t>
-  </si>
-  <si>
-    <t>Given a feature matrix `X` of shape $100 \times 5$, what is the shape of the corresponding label vector `y`?</t>
-  </si>
-  <si>
-    <t>(1,5)</t>
-  </si>
-  <si>
-    <t>(100,1)</t>
-  </si>
-  <si>
-    <t>(100,)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5,1) </t>
-  </si>
-  <si>
-    <t>What is the output of the following code snippet?
-```{python eval=FALSE}
-from sklearn.metrics import accuracy_score
-y_true = [1, 0, 1, 1, 0]
-y_pred = [1, 0, 0, 1, 1]
-print(accuracy_score(y_true, y_pred))
-```</t>
-  </si>
-  <si>
-    <t>There will be an error message because no model has been fitted.</t>
-  </si>
-  <si>
-    <t>A Incorrect.
-B The function only requires a `ytrue` and a `ypred` array. It will still run as per normal.
-C Incorrect.
-D Correct - accuracy is the number of correct predictions (3) divided by the number of 
-  total predictions made (5).</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Which of the following scikit-learn models is/are typically used for regression problems (not classification)?</t>
-  </si>
-  <si>
-    <t>Decision Tree Regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Logistic Regression</t>
-  </si>
-  <si>
-    <t>Linear Regression</t>
-  </si>
-  <si>
-    <t>Naive Bayes</t>
-  </si>
-  <si>
-    <t>A Correct
-B This is a model for performing binary classification.
-C Correct.
-D This is used for classification.</t>
-  </si>
-  <si>
-    <t>A, C</t>
-  </si>
-  <si>
-    <t>The correct leaf is the eighth from the left. Note that darker blue indicates higher probability of red, and darker orange indicates higher probability of white. In the terminal node, there are 5 instances of white and 987 instances of red. Hence the estimated probability is 5/(987 + 5) = 0.005.
-A is the estimated probability of red.
-B Correct
-C Incorrect - uses gini, which is not probability.
-D Incorrect - uses gini, which is not probability.</t>
-  </si>
-  <si>
-    <t>Consider a new wine with the following features, but unknown `type`. 
-```{python, echo=FALSE}
-wine2.sample(n=1, random_state=2002).iloc[:, 0:11].T
-```
-Apply the decision tree rules to the above features to estimate the probability that the wine is *white*.</t>
-  </si>
-  <si>
-    <t>```{r echo=FALSE}
-library(reticulate)
-tmp_out &lt;- include_supplement("venv_paths.csv")
-tmp_out &lt;- include_supplement("winequality-red.csv", dir="../data/wine+quality/")
-tmp_out &lt;- include_supplement("winequality-white.csv", dir="../data/wine+quality/")
-tmp_out &lt;- include_supplement("wine_tree.png", dir="figs/")
-venv_paths &lt;- read.csv("venv_paths.csv")
-id &lt;- match(Sys.info()["nodename"], venv_paths$nodename)
-use_virtualenv(venv_paths$path[id])
-```
-```{python echo=FALSE}
-import pandas as pd
-import numpy as np
-from sklearn import tree
-from sklearn.model_selection import train_test_split
-wine_red = pd.read_csv("winequality-red.csv", delimiter=";" )
-wine_red['type'] = "red"
-wine_white = pd.read_csv("winequality-white.csv", delimiter=";")
-wine_white['type'] = "white"
-# remove spaces in column names:
-col_names = ['fixed_acidity', 'volatile_acidity', 'citric_acid', 'residual_sugar',
-             'chlorides', 'free_sulfur_dioxide', 'total_sulfur_dioxide',
-             'density', 'pH', 'sulphates', 'alcohol', 'quality', 'type']
-wine2 = pd.concat([wine_red, wine_white], ignore_index=True)
-wine2.columns = col_names
-```
-The (red and white) wine quality datasets from the unsupervised learning topic have been merged into a single dataframe with 6497 rows. A decision tree classifier has been fit to the dataset as follows:
-```{python}
-wine2.shape
-wine2.type.value_counts()
-y = [1 if x=="red" else 0 for x in wine2.type]
-X = wine2.iloc[:, 0:11]
-X_train,X_test,y_train,y_test = train_test_split(X, y, test_size=0.2,  random_state=14, stratify=y)
-```
-The resulting decision tree consists of the following [rules](wine_tree.png):
-```{r echo=FALSE, out.width="2000px", fig.align="center", fig.cap="Decision tree"}
-knitr::include_graphics("wine_tree.png")
-```</t>
-  </si>
-  <si>
-    <t>The correct leaf is the eighth from the right. Note that darker blue indicates 
-higher probability of red, and darker orange indicates higher probability of 
-white. In the terminal node, there are 3617 instances of white and 30 instances 
-of red. Hence the estimated probability is 30/(30+3617) = 0.008.
-A Correct
-B This is the estimated probability of white.
-C Incorrect - uses gini, which is not probability.
-D Incorrect - uses gini, which is not probability.</t>
-  </si>
-  <si>
-    <t>Compute the following metrics for **white wine** category, to 3 d.p.:
-* precision: ______(1)______
-* recall:    ______(2)______
-* accuracy:  ______(3)______</t>
-  </si>
-  <si>
-    <t>SRQ</t>
-  </si>
-  <si>
-    <t>1. 3908/(3908+60) = 0.985
-2. 3908/(3908+10) = 0.997
-3. (3908+1219)/(5197) = 0.987</t>
-  </si>
-  <si>
-    <t>1. 0.985,
-2. 0.997
-3. 0.987</t>
-  </si>
-  <si>
-    <t>```{r echo=FALSE}
-library(reticulate)
-tmp_out &lt;- include_supplement("venv_paths.csv")
-tmp_out &lt;- include_supplement("winequality-red.csv", dir="../data/wine+quality/")
-tmp_out &lt;- include_supplement("winequality-white.csv", dir="../data/wine+quality/")
-venv_paths &lt;- read.csv("venv_paths.csv")
-id &lt;- match(Sys.info()["nodename"], venv_paths$nodename)
-use_virtualenv(venv_paths$path[id])
-```
-```{python echo=FALSE}
-import pandas as pd
-import numpy as np
-from sklearn import tree
-from sklearn.model_selection import train_test_split
-from sklearn.metrics import ConfusionMatrixDisplay
-wine_red = pd.read_csv("winequality-red.csv", delimiter=";" )
-wine_red['type'] = "red"
-wine_white = pd.read_csv("winequality-white.csv", delimiter=";")
-wine_white['type'] = "white"
-# remove spaces in column names:
-col_names = ['fixed_acidity', 'volatile_acidity', 'citric_acid', 'residual_sugar',
-             'chlorides', 'free_sulfur_dioxide', 'total_sulfur_dioxide',
-             'density', 'pH', 'sulphates', 'alcohol', 'quality', 'type']
-wine2 = pd.concat([wine_red, wine_white], ignore_index=True)
-wine2.columns = col_names
-```
-Question
-========
-The (red and white) wine quality datasets from the unsupervised learning topic 
-have been merged into a single dataframe with 6497 rows. A decision tree 
-classifier has been fit to the dataset as follows:
-```{python fig.align="center", fig.cap="Confusion matrix"}
-y = [1 if x=="red" else 0 for x in wine2.type]
-X = wine2.iloc[:, 0:11]
-X_train,X_test,y_train,y_test = train_test_split(X, y, test_size=0.2, random_state=14, stratify=y)
-clf = tree.DecisionTreeClassifier(max_depth=4)
-clf.fit(X_train, y_train)
-y_pred_train = clf.predict(X_train)
-ConfusionMatrixDisplay.from_predictions(y_train, y_pred_train, labels=clf.classes_, cmap='bone');
-```</t>
-  </si>
-  <si>
-    <t>venv_paths.csv, winequality-white.csv, winequality-red.csv</t>
-  </si>
-  <si>
-    <t>Supervised Learning, Data Manipulation</t>
-  </si>
-  <si>
-    <t>Data Manipulation, Basic Concepts in Statistics</t>
-  </si>
-  <si>
-    <t>Model Validation, Supervised Learning, Data Manipulation</t>
-  </si>
-  <si>
-    <t>Supervised Learning,Regression</t>
-  </si>
-  <si>
-    <t>Supervised Learning, Decision Tree, Model Validation</t>
-  </si>
-  <si>
-    <t>Consider a new wine with the following features, but unknown `type`. 
-```{python, echo=FALSE}
-wine2.sample(n=1, random_state=22).iloc[:, 0:11].T
-```
-Apply the decision tree rules to the above features to estimate the probability that the wine is *red*.</t>
-  </si>
-  <si>
-    <t>Supervised Learning, Decision Trees, Model Validation, Basic Concepts in Statistics</t>
+    <t>Context ID</t>
   </si>
 </sst>
 </file>
@@ -713,7 +403,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -721,19 +411,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -748,19 +438,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1095,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD344A99-2334-9F42-80E8-59AFD62EE11D}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="65.1640625" style="1" customWidth="1"/>
@@ -1103,14 +788,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -1118,10 +803,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -1129,32 +814,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" t="s">
-        <v>127</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1164,66 +827,66 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{481B256A-7EE5-8644-A3E2-ED4B6945B4AB}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="112.83203125" style="1" customWidth="1"/>
     <col min="6" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="44.33203125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="70.6640625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="42.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.33203125" customWidth="1"/>
+    <col min="12" max="12" width="70.6640625" customWidth="1"/>
+    <col min="15" max="15" width="42.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -1234,35 +897,35 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" s="2"/>
+      <c r="K2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="4" t="s">
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" t="s">
         <v>24</v>
       </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>27</v>
+      <c r="O2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -1273,10 +936,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>95.016900000000007</v>
@@ -1293,17 +956,17 @@
       <c r="J3" s="2">
         <v>2.5200000000000001E-71</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
       <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1314,34 +977,34 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="N4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" t="s">
         <v>25</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -1352,19 +1015,19 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="K5" t="s">
+        <v>36</v>
+      </c>
       <c r="N5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
+      </c>
+      <c r="O5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -1375,19 +1038,19 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="3" t="s">
+      <c r="N6" t="s">
         <v>45</v>
       </c>
-      <c r="N6" t="s">
-        <v>46</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>50</v>
+      <c r="O6" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -1398,19 +1061,19 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="s">
         <v>48</v>
       </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="N7" t="s">
-        <v>46</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="O7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="221" x14ac:dyDescent="0.2">
@@ -1421,19 +1084,19 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="N8" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>56</v>
+        <v>24</v>
+      </c>
+      <c r="O8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -1444,34 +1107,34 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" t="s">
         <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" t="s">
-        <v>46</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="221" x14ac:dyDescent="0.2">
@@ -1482,19 +1145,19 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" t="s">
         <v>64</v>
       </c>
-      <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="N10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" t="s">
         <v>74</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1505,378 +1168,37 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
         <v>66</v>
       </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>67</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>68</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>69</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>70</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" t="s">
         <v>71</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="N11" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="170" x14ac:dyDescent="0.2">
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" t="s">
-        <v>86</v>
-      </c>
-      <c r="I13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N13" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="238" x14ac:dyDescent="0.2">
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" t="s">
-        <v>95</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="85" x14ac:dyDescent="0.2">
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" t="s">
-        <v>98</v>
-      </c>
-      <c r="H15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I15" t="s">
-        <v>100</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="N15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" t="s">
-        <v>103</v>
-      </c>
-      <c r="G16" t="s">
-        <v>104</v>
-      </c>
-      <c r="H16" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" t="s">
-        <v>106</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N16" t="s">
-        <v>25</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="153" x14ac:dyDescent="0.2">
-      <c r="B17">
-        <v>6</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17">
-        <v>0.2</v>
-      </c>
-      <c r="G17" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17">
-        <v>0.4</v>
-      </c>
-      <c r="I17">
-        <v>0.6</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="N17" t="s">
-        <v>46</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="68" x14ac:dyDescent="0.2">
-      <c r="B18">
-        <v>7</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" t="s">
-        <v>113</v>
-      </c>
-      <c r="H18" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" t="s">
-        <v>115</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="N18" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="153" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19">
-        <v>8</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19">
-        <v>0.995</v>
-      </c>
-      <c r="G19">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H19">
-        <v>0.01</v>
-      </c>
-      <c r="I19">
-        <v>0.99</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="N19" t="s">
-        <v>46</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="153" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>3</v>
-      </c>
-      <c r="B20">
-        <v>9</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G20">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="H20">
-        <v>1.6E-2</v>
-      </c>
-      <c r="I20">
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="N20" t="s">
-        <v>46</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="85" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>4</v>
-      </c>
-      <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" t="s">
-        <v>123</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="N21" t="s">
-        <v>46</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>134</v>
+        <v>24</v>
+      </c>
+      <c r="O11" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
